--- a/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,68; 100,0</t>
+          <t>52,62; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 88,15</t>
+          <t>51,88; 87,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,24; 92,66</t>
+          <t>40,28; 92,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,49; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,11; 93,9</t>
+          <t>55,52; 93,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,94; 88,85</t>
+          <t>53,76; 89,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,97; 100,0</t>
+          <t>48,77; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,63; 100,0</t>
+          <t>56,97; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,04; 95,75</t>
+          <t>63,52; 95,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,76; 84,01</t>
+          <t>58,0; 84,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54,51; 91,44</t>
+          <t>56,93; 91,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,36; 100,0</t>
+          <t>74,61; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 53,46</t>
+          <t>6,89; 49,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49,01; 89,0</t>
+          <t>45,87; 88,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,27</t>
+          <t>0,0; 81,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,13; 90,29</t>
+          <t>33,46; 90,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,75; 88,37</t>
+          <t>46,6; 88,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,63; 94,69</t>
+          <t>55,24; 94,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 79,36</t>
+          <t>21,37; 77,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,63; 66,1</t>
+          <t>32,24; 67,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60,07; 86,39</t>
+          <t>59,72; 88,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,21; 91,32</t>
+          <t>37,15; 91,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,39; 76,04</t>
+          <t>36,88; 76,3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 83,17</t>
+          <t>13,36; 83,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,63; 86,14</t>
+          <t>32,99; 85,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 87,54</t>
+          <t>13,57; 86,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,49; 100,0</t>
+          <t>50,14; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,94; 85,74</t>
+          <t>14,41; 85,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,84; 88,41</t>
+          <t>22,14; 88,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,56</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 85,26</t>
+          <t>29,67; 85,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 76,79</t>
+          <t>23,7; 77,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 78,58</t>
+          <t>36,99; 77,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 75,46</t>
+          <t>11,31; 71,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,26; 88,05</t>
+          <t>47,21; 85,76</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,92; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,82; 88,72</t>
+          <t>31,73; 89,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,77; 85,63</t>
+          <t>23,39; 81,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,7; 100,0</t>
+          <t>50,53; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 78,25</t>
+          <t>12,32; 76,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,57; 100,0</t>
+          <t>53,05; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,53; 100,0</t>
+          <t>61,41; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74,33; 100,0</t>
+          <t>75,62; 100,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,98; 86,53</t>
+          <t>37,26; 86,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54,92; 90,68</t>
+          <t>56,74; 90,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,63; 93,63</t>
+          <t>57,15; 94,08</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 88,41</t>
+          <t>14,43; 88,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,9; 100,0</t>
+          <t>30,73; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,48; 88,08</t>
+          <t>19,55; 88,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,43</t>
+          <t>0,0; 71,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,36; 82,63</t>
+          <t>23,46; 82,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,24; 100,0</t>
+          <t>39,35; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 70,28</t>
+          <t>19,76; 71,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,11; 82,57</t>
+          <t>38,08; 82,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,22; 93,92</t>
+          <t>43,98; 94,04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1421,64 +1422,64 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,49; 100,0</t>
+          <t>38,73; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 64,16</t>
+          <t>8,87; 71,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,6; 87,47</t>
+          <t>14,7; 87,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,77</t>
+          <t>0,0; 62,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,87; 76,74</t>
+          <t>16,01; 72,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,57</t>
+          <t>0,0; 58,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,18; 79,59</t>
+          <t>33,95; 81,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,96; 69,19</t>
+          <t>9,92; 64,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37,86; 79,47</t>
+          <t>33,38; 77,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,83; 50,87</t>
+          <t>12,13; 48,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,11; 76,04</t>
+          <t>37,1; 77,38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,79; 92,85</t>
+          <t>49,19; 92,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,75; 78,6</t>
+          <t>35,68; 78,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,57; 92,62</t>
+          <t>43,16; 92,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71,84; 100,0</t>
+          <t>72,49; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,52; 82,76</t>
+          <t>45,76; 86,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,71; 84,08</t>
+          <t>43,4; 83,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,57; 60,83</t>
+          <t>13,24; 62,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>45,06; 81,47</t>
+          <t>43,29; 81,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,33; 83,54</t>
+          <t>55,4; 85,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,17; 74,69</t>
+          <t>46,45; 76,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,9; 69,96</t>
+          <t>33,92; 71,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,42; 84,05</t>
+          <t>55,97; 85,36</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,38; 88,97</t>
+          <t>44,61; 89,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,93; 66,1</t>
+          <t>29,12; 66,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 67,0</t>
+          <t>9,39; 66,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,69; 85,94</t>
+          <t>31,79; 89,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>53,9; 84,01</t>
+          <t>55,39; 85,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,54; 73,84</t>
+          <t>41,25; 74,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,5; 72,1</t>
+          <t>22,47; 71,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,87; 77,18</t>
+          <t>14,52; 76,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,97; 82,66</t>
+          <t>57,92; 82,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41,39; 65,78</t>
+          <t>40,56; 65,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,03; 62,62</t>
+          <t>21,69; 63,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,31; 73,43</t>
+          <t>33,02; 73,4</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54,32; 74,63</t>
+          <t>53,79; 76,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55,68; 73,21</t>
+          <t>56,49; 73,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42,92; 66,39</t>
+          <t>43,48; 67,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65,69; 83,67</t>
+          <t>65,19; 84,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,47; 75,05</t>
+          <t>58,46; 74,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,12; 70,26</t>
+          <t>52,57; 69,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,52; 68,46</t>
+          <t>44,39; 69,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59,11; 79,0</t>
+          <t>58,95; 79,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,77</t>
+          <t>59,94; 73,37</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56,92; 68,92</t>
+          <t>57,16; 69,18</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47,09; 63,67</t>
+          <t>48,02; 63,87</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>64,47; 79,49</t>
+          <t>65,01; 78,91</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado al nivel de asistencia al cole/guardería (tasa de respuesta: 98,55%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5142</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10542</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4855</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9157</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12230</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11512</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14299</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22772</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>24741</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3065; 5825</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7607; 12867</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2788; 6435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6301; 10659</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8947; 14959</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4383; 8986</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7810; 13709</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10909; 16465</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18155; 26420</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9056; 14536</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>20098; 26938</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7836</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9319</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10356</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>17426</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4578</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>9415</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>695; 4967</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5223; 10108</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2974</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2573; 6924</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5179; 9811</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6579; 11257</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1873; 6802</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6834; 14407</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13912; 20662</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2614; 6426</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6067; 12551</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2139</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9278</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2959</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11141</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>595; 3704</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3052; 7947</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>632; 4043</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3612; 7204</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>634; 3775</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1363; 5457</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2710</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2520; 7225</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2099; 6850</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5699; 11995</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>834; 5286</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7410; 13462</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6338</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5027</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6132</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11886</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14296</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24478</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2895; 8130</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2172; 7547</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3438; 6804</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>955; 5958</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5075; 9566</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13634; 22202</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9496; 12558</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4461; 10365</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10605; 16957</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>17994; 29623</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2974</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4159</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8146</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>756; 4628</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1645; 5355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>626; 2837</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3517</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1838; 6460</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1633; 4151</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2000; 7252</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5022; 10930</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3233; 6913</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8695</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2076</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2254; 5820</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>653; 5262</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>615; 3643</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3149</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1451; 6546</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4649</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>3921; 9372</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>704; 4604</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>4968; 11581</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1858; 7358</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5837; 12171</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7646</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10290</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>11217</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>14273</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>17937</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>18691</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8598</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>23744</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4815; 9082</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4628; 10234</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3192; 6868</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7560; 10428</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6892; 13042</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7456; 14420</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1218; 5787</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>9567; 17930</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>13768; 21244</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14005; 23017</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5627; 11896</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>18207; 27765</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8920</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>16346</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>12738</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>24555</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>21658</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6646</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8702</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>5130; 10273</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>5411; 12333</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>697; 4958</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2649; 7463</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>12659; 19591</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>9082; 16400</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1880; 6023</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1170; 6129</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>19899; 28267</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>16467; 26772</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3425; 9954</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5414; 12033</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>35751</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>53548</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>26016</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>48125</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>68522</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>90659</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>114287</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>55336</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>116648</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>29434; 41587</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>46455; 60424</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>20490; 31947</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>41428; 53707</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>47642; 60804</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>51812; 68059</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>22837; 35626</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>58373; 79100</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>81647; 99940</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>103352; 125068</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>47336; 62952</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>105685; 128287</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,62; 100,0</t>
+          <t>52,51; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,88; 87,76</t>
+          <t>50,48; 87,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,28; 92,96</t>
+          <t>38,33; 93,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,52; 93,92</t>
+          <t>55,84; 94,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,76; 89,88</t>
+          <t>50,2; 89,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,77; 100,0</t>
+          <t>51,85; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,97; 100,0</t>
+          <t>55,58; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63,52; 95,87</t>
+          <t>65,43; 95,96</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,0; 84,4</t>
+          <t>58,64; 84,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,93; 91,38</t>
+          <t>53,73; 90,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,61; 100,0</t>
+          <t>75,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 49,25</t>
+          <t>6,3; 51,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,87; 88,77</t>
+          <t>44,66; 88,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,89</t>
+          <t>0,0; 81,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,46; 90,04</t>
+          <t>33,18; 89,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,6; 88,27</t>
+          <t>46,9; 88,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,24; 94,52</t>
+          <t>55,12; 94,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,37; 77,63</t>
+          <t>19,27; 77,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,24; 67,96</t>
+          <t>30,82; 65,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59,72; 88,69</t>
+          <t>59,52; 86,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 91,33</t>
+          <t>29,73; 91,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 76,3</t>
+          <t>35,96; 75,39</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 83,2</t>
+          <t>13,32; 83,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32,99; 85,89</t>
+          <t>35,13; 85,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,57; 86,81</t>
+          <t>13,62; 86,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,14; 100,0</t>
+          <t>55,97; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,14; 88,66</t>
+          <t>21,71; 88,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,67; 85,06</t>
+          <t>25,69; 85,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23,7; 77,35</t>
+          <t>24,07; 77,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,99; 77,84</t>
+          <t>38,52; 78,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 71,76</t>
+          <t>10,96; 73,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,21; 85,76</t>
+          <t>50,24; 88,13</t>
         </is>
       </c>
     </row>
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,73; 89,08</t>
+          <t>36,8; 93,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 81,27</t>
+          <t>25,59; 81,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,53; 100,0</t>
+          <t>59,55; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 76,83</t>
+          <t>10,94; 80,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,05; 100,0</t>
+          <t>51,41; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61,41; 100,0</t>
+          <t>62,5; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75,62; 100,0</t>
+          <t>69,65; 100,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,26; 86,58</t>
+          <t>35,99; 87,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,74; 90,72</t>
+          <t>55,67; 91,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,15; 94,08</t>
+          <t>55,51; 94,11</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 88,38</t>
+          <t>13,6; 88,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,73; 100,0</t>
+          <t>30,75; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 88,67</t>
+          <t>19,61; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,99</t>
+          <t>0,0; 71,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,46; 82,47</t>
+          <t>24,47; 81,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,35; 100,0</t>
+          <t>39,85; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,76; 71,64</t>
+          <t>20,93; 72,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,08; 82,88</t>
+          <t>37,77; 80,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,98; 94,04</t>
+          <t>46,04; 93,46</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,73; 100,0</t>
+          <t>38,39; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,87; 71,47</t>
+          <t>9,62; 64,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,7; 87,13</t>
+          <t>19,98; 87,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,79</t>
+          <t>0,0; 62,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 72,24</t>
+          <t>23,23; 77,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,42</t>
+          <t>0,0; 59,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,95; 81,15</t>
+          <t>33,16; 78,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 64,93</t>
+          <t>9,3; 64,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33,38; 77,82</t>
+          <t>38,64; 77,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,13; 48,03</t>
+          <t>13,51; 49,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,1; 77,38</t>
+          <t>35,38; 77,42</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,19; 92,78</t>
+          <t>49,69; 92,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,68; 78,91</t>
+          <t>32,25; 79,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,16; 92,87</t>
+          <t>44,8; 92,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72,49; 100,0</t>
+          <t>69,03; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,76; 86,58</t>
+          <t>45,7; 86,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,4; 83,93</t>
+          <t>44,68; 82,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 62,93</t>
+          <t>12,38; 57,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,29; 81,13</t>
+          <t>44,14; 83,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>55,4; 85,49</t>
+          <t>58,04; 83,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46,45; 76,34</t>
+          <t>45,83; 75,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33,92; 71,7</t>
+          <t>32,01; 71,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,97; 85,36</t>
+          <t>55,73; 85,98</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>44,61; 89,34</t>
+          <t>45,81; 89,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,12; 66,37</t>
+          <t>30,06; 65,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,39; 66,8</t>
+          <t>9,63; 65,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31,79; 89,59</t>
+          <t>33,97; 86,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,39; 85,72</t>
+          <t>54,01; 83,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,25; 74,49</t>
+          <t>39,46; 74,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,47; 71,98</t>
+          <t>23,38; 75,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,52; 76,01</t>
+          <t>11,33; 70,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,92; 82,28</t>
+          <t>56,82; 81,67</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40,56; 65,95</t>
+          <t>39,96; 65,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,69; 63,04</t>
+          <t>24,2; 64,54</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,02; 73,4</t>
+          <t>33,43; 74,44</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53,79; 76,0</t>
+          <t>54,79; 75,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56,49; 73,47</t>
+          <t>56,48; 72,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43,48; 67,8</t>
+          <t>43,74; 66,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65,19; 84,51</t>
+          <t>65,62; 84,6</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,46; 74,61</t>
+          <t>59,33; 75,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,57; 69,06</t>
+          <t>53,37; 69,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,39; 69,25</t>
+          <t>46,18; 68,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58,95; 79,88</t>
+          <t>58,71; 79,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>59,94; 73,37</t>
+          <t>60,06; 72,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57,16; 69,18</t>
+          <t>57,1; 68,75</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48,02; 63,87</t>
+          <t>48,12; 64,71</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,01; 78,91</t>
+          <t>65,01; 80,01</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3065; 5825</t>
+          <t>3059; 5825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7607; 12867</t>
+          <t>7401; 12854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2788; 6435</t>
+          <t>2653; 6447</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,42 +2229,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6301; 10659</t>
+          <t>6337; 10672</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8947; 14959</t>
+          <t>8354; 14918</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4383; 8986</t>
+          <t>4659; 8986</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7810; 13709</t>
+          <t>7619; 13709</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10909; 16465</t>
+          <t>11237; 16480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18155; 26420</t>
+          <t>18358; 26598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9056; 14536</t>
+          <t>8547; 14445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20098; 26938</t>
+          <t>20333; 26938</t>
         </is>
       </c>
     </row>
@@ -2417,32 +2417,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>695; 4967</t>
+          <t>635; 5231</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5223; 10108</t>
+          <t>5085; 10130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 2978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2573; 6924</t>
+          <t>2551; 6904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5179; 9811</t>
+          <t>5212; 9813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6579; 11257</t>
+          <t>6565; 11273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1873; 6802</t>
+          <t>1689; 6772</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6834; 14407</t>
+          <t>6533; 13817</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13912; 20662</t>
+          <t>13866; 20196</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2614; 6426</t>
+          <t>2092; 6406</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6067; 12551</t>
+          <t>5915; 12403</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>595; 3704</t>
+          <t>593; 3716</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3052; 7947</t>
+          <t>3251; 7947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632; 4043</t>
+          <t>634; 4037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3612; 7204</t>
+          <t>4032; 7204</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1363; 5457</t>
+          <t>1336; 5450</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2520; 7225</t>
+          <t>2182; 7254</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2099; 6850</t>
+          <t>2131; 6861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5699; 11995</t>
+          <t>5935; 12148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>834; 5286</t>
+          <t>807; 5423</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7410; 13462</t>
+          <t>7886; 13834</t>
         </is>
       </c>
     </row>
@@ -2843,52 +2843,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2895; 8130</t>
+          <t>3358; 8539</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2172; 7547</t>
+          <t>2376; 7565</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3438; 6804</t>
+          <t>4052; 6804</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>955; 5958</t>
+          <t>848; 6265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5075; 9566</t>
+          <t>4918; 9566</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13634; 22202</t>
+          <t>13876; 22202</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9496; 12558</t>
+          <t>8747; 12558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4461; 10365</t>
+          <t>4309; 10443</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10605; 16957</t>
+          <t>10406; 17009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17994; 29623</t>
+          <t>17478; 29634</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>756; 4628</t>
+          <t>712; 4659</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1645; 5355</t>
+          <t>1647; 5355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,17 +3056,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>626; 2837</t>
+          <t>627; 3200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>0; 3493</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1838; 6460</t>
+          <t>1917; 6421</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1633; 4151</t>
+          <t>1654; 4151</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2000; 7252</t>
+          <t>2119; 7338</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5022; 10930</t>
+          <t>4981; 10620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3233; 6913</t>
+          <t>3384; 6870</t>
         </is>
       </c>
     </row>
@@ -3254,57 +3254,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2254; 5820</t>
+          <t>2234; 5820</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>653; 5262</t>
+          <t>709; 4720</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>615; 3643</t>
+          <t>835; 3669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3149</t>
+          <t>0; 3147</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1451; 6546</t>
+          <t>2105; 7024</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3921; 9372</t>
+          <t>3830; 9043</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>704; 4604</t>
+          <t>659; 4591</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4968; 11581</t>
+          <t>5751; 11590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1858; 7358</t>
+          <t>2070; 7599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5837; 12171</t>
+          <t>5565; 12178</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4815; 9082</t>
+          <t>4864; 9088</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4628; 10234</t>
+          <t>4183; 10257</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3192; 6868</t>
+          <t>3313; 6862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7560; 10428</t>
+          <t>7199; 10428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6892; 13042</t>
+          <t>6884; 13031</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7456; 14420</t>
+          <t>7677; 14109</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1218; 5787</t>
+          <t>1138; 5285</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9567; 17930</t>
+          <t>9754; 18355</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13768; 21244</t>
+          <t>14423; 20839</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14005; 23017</t>
+          <t>13817; 22677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5627; 11896</t>
+          <t>5311; 11850</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18207; 27765</t>
+          <t>18127; 27968</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5130; 10273</t>
+          <t>5268; 10308</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5411; 12333</t>
+          <t>5586; 12258</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>697; 4958</t>
+          <t>715; 4827</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2649; 7463</t>
+          <t>2829; 7200</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12659; 19591</t>
+          <t>12345; 19179</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9082; 16400</t>
+          <t>8688; 16401</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1880; 6023</t>
+          <t>1956; 6300</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1170; 6129</t>
+          <t>914; 5721</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19899; 28267</t>
+          <t>19520; 28054</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16467; 26772</t>
+          <t>16222; 26398</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3425; 9954</t>
+          <t>3821; 10190</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5414; 12033</t>
+          <t>5480; 12202</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29434; 41587</t>
+          <t>29982; 41303</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46455; 60424</t>
+          <t>46450; 59996</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20490; 31947</t>
+          <t>20610; 31256</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41428; 53707</t>
+          <t>41701; 53764</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>47642; 60804</t>
+          <t>48345; 61351</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>51812; 68059</t>
+          <t>52596; 68499</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22837; 35626</t>
+          <t>23760; 35233</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>58373; 79100</t>
+          <t>58136; 79103</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81647; 99940</t>
+          <t>81807; 99351</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103352; 125068</t>
+          <t>103227; 124300</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47336; 62952</t>
+          <t>47433; 63783</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>105685; 128287</t>
+          <t>105698; 130081</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP09B01-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>80,96%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>88,27%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>70,13%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>80,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83,97%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>83,26%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,51; 100,0</t>
+          <t>55,11; 93,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,48; 87,67</t>
+          <t>50,94; 88,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,33; 93,14</t>
+          <t>48,97; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>62,57; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51,68; 100,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>51,59; 88,15</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38,24; 92,66</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,84; 94,04</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,2; 89,63</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,85; 100,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>55,58; 100,0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65,43; 95,96</t>
+          <t>62,04; 95,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58,64; 84,97</t>
+          <t>58,76; 84,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,73; 90,8</t>
+          <t>54,51; 91,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,48; 100,0</t>
+          <t>73,95; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>24,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>71,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>32,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>64,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>70,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>61,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 51,87</t>
+          <t>46,75; 88,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,66; 88,97</t>
+          <t>56,63; 94,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,18; 89,78</t>
+          <t>24,9; 82,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,9; 88,29</t>
+          <t>6,18; 53,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,12; 94,65</t>
+          <t>49,01; 89,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 67,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,27; 77,29</t>
+          <t>31,64; 90,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,82; 65,17</t>
+          <t>31,63; 66,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59,52; 86,69</t>
+          <t>60,07; 86,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,73; 91,04</t>
+          <t>32,21; 91,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,96; 75,39</t>
+          <t>39,33; 79,55</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56,86%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24,73%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59,3%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>48,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>63,52%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>49,15%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 83,47</t>
+          <t>13,94; 85,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,13; 85,89</t>
+          <t>21,84; 88,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,62; 86,69</t>
+          <t>0,0; 75,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55,97; 100,0</t>
+          <t>29,68; 84,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 85,72</t>
+          <t>13,32; 83,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 88,54</t>
+          <t>38,63; 86,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>8,98; 87,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 85,41</t>
+          <t>50,76; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,07; 77,47</t>
+          <t>22,22; 76,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,52; 78,84</t>
+          <t>39,1; 78,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 73,61</t>
+          <t>11,45; 75,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,24; 88,13</t>
+          <t>48,48; 87,72</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87,17%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>69,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54,13%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50,7; 100,0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10,38; 78,25</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51,57; 100,0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60,65; 98,94</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36,8; 93,57</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>25,59; 81,46</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>59,55; 100,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>10,94; 80,79</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,41; 100,0</t>
+          <t>36,82; 88,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,5; 100,0</t>
+          <t>23,11; 83,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,65; 100,0</t>
+          <t>74,33; 100,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,99; 87,23</t>
+          <t>37,98; 86,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55,67; 91,0</t>
+          <t>54,92; 90,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,51; 94,11</t>
+          <t>54,73; 92,54</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28,83%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>56,78%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>74,44%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>57,92%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>53,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>54,9%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>61,77%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>43,29%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>61,77%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,6; 88,96</t>
+          <t>0,0; 71,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,75; 100,0</t>
+          <t>23,36; 82,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,61; 100,0</t>
+          <t>54,55; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,5</t>
+          <t>17,15; 88,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,47; 81,97</t>
+          <t>29,9; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,85; 100,0</t>
+          <t>17,01; 87,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,93; 72,5</t>
+          <t>19,26; 70,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,77; 80,53</t>
+          <t>38,11; 82,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,04; 93,46</t>
+          <t>44,38; 93,27</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56,53%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>65,83%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>76,02%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>35,65%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56,59%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,58%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 62,77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22,87; 76,74</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 51,57</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31,69; 79,07</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>38,39; 100,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9,62; 64,12</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>19,98; 87,76</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 62,74</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,23; 77,51</t>
+          <t>38,49; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,35</t>
+          <t>9,13; 64,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,16; 78,3</t>
+          <t>14,96; 86,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,3; 64,73</t>
+          <t>9,96; 69,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,64; 77,88</t>
+          <t>37,86; 79,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,51; 49,6</t>
+          <t>12,83; 50,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,38; 77,42</t>
+          <t>36,0; 75,87</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65,29%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>78,12%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>57,63%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>74,16%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>49,69; 92,84</t>
+          <t>45,52; 82,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,25; 79,09</t>
+          <t>46,71; 84,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,8; 92,8</t>
+          <t>12,57; 60,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69,03; 100,0</t>
+          <t>50,01; 83,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,7; 86,51</t>
+          <t>49,79; 92,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,68; 82,12</t>
+          <t>31,75; 78,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 57,47</t>
+          <t>39,57; 92,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,14; 83,06</t>
+          <t>74,82; 100,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58,04; 83,86</t>
+          <t>55,33; 83,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,83; 75,21</t>
+          <t>46,17; 74,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32,01; 71,42</t>
+          <t>31,9; 69,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,73; 85,98</t>
+          <t>59,23; 86,45</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>71,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>48,01%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>35,64%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>45,81; 89,64</t>
+          <t>53,9; 84,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30,06; 65,97</t>
+          <t>38,54; 73,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,63; 65,03</t>
+          <t>22,5; 72,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,97; 86,44</t>
+          <t>14,57; 77,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,01; 83,92</t>
+          <t>44,38; 88,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,46; 74,5</t>
+          <t>29,93; 66,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,38; 75,29</t>
+          <t>8,86; 67,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,33; 70,96</t>
+          <t>32,26; 87,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56,82; 81,67</t>
+          <t>58,97; 82,66</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39,96; 65,03</t>
+          <t>41,39; 65,78</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,2; 64,54</t>
+          <t>25,03; 62,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,43; 74,44</t>
+          <t>31,11; 73,1</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>54,79; 75,48</t>
+          <t>58,47; 75,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56,48; 72,95</t>
+          <t>54,12; 70,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>43,74; 66,33</t>
+          <t>45,52; 68,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65,62; 84,6</t>
+          <t>60,48; 79,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,33; 75,29</t>
+          <t>54,32; 74,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,37; 69,5</t>
+          <t>55,68; 73,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,18; 68,48</t>
+          <t>42,92; 66,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>58,71; 79,88</t>
+          <t>63,28; 81,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60,06; 72,94</t>
+          <t>60,18; 73,77</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57,1; 68,75</t>
+          <t>56,92; 68,92</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48,12; 64,71</t>
+          <t>47,09; 63,67</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>65,01; 80,01</t>
+          <t>64,01; 78,34</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12230</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>5142</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10542</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4855</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13229</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9157</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12230</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7275</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>17671</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3059; 5825</t>
+          <t>6254; 10657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7401; 12854</t>
+          <t>8478; 14787</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2653; 6447</t>
+          <t>4400; 8986</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>7225; 11546</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3011; 5825</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7563; 12924</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2647; 6414</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6337; 10672</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8354; 14918</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4659; 8986</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7619; 13709</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11237; 16480</t>
+          <t>10655; 16443</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18358; 26598</t>
+          <t>18393; 26299</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8547; 14445</t>
+          <t>8671; 14547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20333; 26938</t>
+          <t>14255; 19277</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7836</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9319</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4192</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2520</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8107</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1174</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4980</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7836</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9319</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9409</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>635; 5231</t>
+          <t>5195; 9821</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5085; 10130</t>
+          <t>6744; 11278</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2551; 6904</t>
+          <t>1864; 6212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5212; 9813</t>
+          <t>623; 5392</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6565; 11273</t>
+          <t>5580; 10133</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2443</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1689; 6772</t>
+          <t>2489; 7143</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6533; 13817</t>
+          <t>6706; 14013</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13866; 20196</t>
+          <t>13994; 20125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2092; 6406</t>
+          <t>2266; 6425</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5915; 12403</t>
+          <t>6038; 12212</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4334</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2139</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5877</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2289</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6087</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11141</t>
+          <t>9772</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>593; 3716</t>
+          <t>614; 3776</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3251; 7947</t>
+          <t>1344; 5442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>634; 4037</t>
+          <t>0; 2048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4032; 7204</t>
+          <t>2169; 6149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>634; 3775</t>
+          <t>593; 3703</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1336; 5450</t>
+          <t>3574; 7971</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2710</t>
+          <t>418; 4077</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2182; 7254</t>
+          <t>3344; 6587</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2131; 6861</t>
+          <t>1968; 6800</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5935; 12148</t>
+          <t>6025; 12108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>807; 5423</t>
+          <t>844; 5559</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7886; 13834</t>
+          <t>6738; 12191</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6132</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16919</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5754</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4217</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6338</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5027</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6132</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3404</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7958</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>22400</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>3450; 6804</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>805; 6069</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4933; 9566</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11771; 19202</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3358; 8539</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2376; 7565</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>4052; 6804</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>848; 6265</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4918; 9566</t>
+          <t>3360; 8097</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13876; 22202</t>
+          <t>2339; 8499</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8747; 12558</t>
+          <t>9334; 12558</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4309; 10443</t>
+          <t>4547; 10359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10406; 17009</t>
+          <t>10266; 16951</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17478; 29634</t>
+          <t>16164; 27329</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4159</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3564</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2974</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3986</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4159</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5398</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>712; 4659</t>
+          <t>0; 3489</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1647; 5355</t>
+          <t>1830; 6472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,17 +3056,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>627; 3200</t>
+          <t>2256; 4135</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>898; 4630</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1917; 6421</t>
+          <t>1601; 5355</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1654; 4151</t>
+          <t>568; 2916</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2119; 7338</t>
+          <t>1950; 7113</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4981; 10620</t>
+          <t>5026; 10889</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3384; 6870</t>
+          <t>3318; 6973</t>
         </is>
       </c>
     </row>
@@ -3123,32 +3123,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4424</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2366</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4271</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7965</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>0; 3149</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2073; 6954</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3044; 7597</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2076</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>2234; 5820</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>709; 4720</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>835; 3669</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3147</t>
-        </is>
-      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2105; 7024</t>
+          <t>2240; 5820</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>672; 4723</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3830; 9043</t>
+          <t>670; 3882</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>659; 4591</t>
+          <t>707; 4907</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5751; 11590</t>
+          <t>5634; 11826</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2070; 7599</t>
+          <t>1966; 7793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5565; 12178</t>
+          <t>5071; 10688</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10290</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11217</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14260</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>7646</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7474</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5484</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9471</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10290</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>11217</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3114</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>24108</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4864; 9088</t>
+          <t>6857; 12466</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4183; 10257</t>
+          <t>8026; 14445</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3313; 6862</t>
+          <t>1156; 5594</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7199; 10428</t>
+          <t>10536; 17558</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6884; 13031</t>
+          <t>4874; 9088</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7677; 14109</t>
+          <t>4118; 10195</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1138; 5285</t>
+          <t>2926; 6849</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9754; 18355</t>
+          <t>7991; 10680</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14423; 20839</t>
+          <t>13751; 20761</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13817; 22677</t>
+          <t>13921; 22520</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5311; 11850</t>
+          <t>5292; 11607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>18127; 27968</t>
+          <t>18805; 27446</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>16346</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12738</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>8210</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>8920</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2645</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>16346</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12738</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8658</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5268; 10308</t>
+          <t>12318; 19201</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5586; 12258</t>
+          <t>8486; 16257</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>715; 4827</t>
+          <t>1882; 6032</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2829; 7200</t>
+          <t>1211; 6422</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12345; 19179</t>
+          <t>5103; 10230</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8688; 16401</t>
+          <t>5561; 12282</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1956; 6300</t>
+          <t>657; 4973</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>914; 5721</t>
+          <t>2670; 7211</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19520; 28054</t>
+          <t>20257; 28394</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16222; 26398</t>
+          <t>16803; 26704</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3821; 10190</t>
+          <t>3953; 9888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5480; 12202</t>
+          <t>5160; 12123</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>29982; 41303</t>
+          <t>47648; 61161</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>46450; 59996</t>
+          <t>53340; 69245</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20610; 31256</t>
+          <t>23419; 35223</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41701; 53764</t>
+          <t>53751; 70273</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>48345; 61351</t>
+          <t>29720; 40835</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>52596; 68499</t>
+          <t>45792; 60211</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23760; 35233</t>
+          <t>20224; 31287</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>58136; 79103</t>
+          <t>37389; 48108</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>81807; 99351</t>
+          <t>81973; 100480</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103227; 124300</t>
+          <t>102905; 124602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47433; 63783</t>
+          <t>46415; 62759</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>105698; 130081</t>
+          <t>94707; 115901</t>
         </is>
       </c>
     </row>
